--- a/data_extactor/batch_10_fa/batch_0061_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0061_fa.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | مدیریت و سازماندهی | روان‌شناسی | پرسنل و منابع انسانی | رایانه‌ها و الکترونیک | فروش و بازاریابی | زیست‌شناسی | فلسفه و الهیات | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | روان‌شناسی | پرسنل و منابع انسانی | رایانه و الکترونیک | فروش و بازاریابی | زیست‌شناسی | فلسفه و الهیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | بحث‌های چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، با تهویه مطبوع | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | ایمیل</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | ایمیل</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون | پزشکان قانونی | اپراتورهای کوره مرده‌سوزی | مدیران فعالیت‌ها و آموزش‌های مذهبی | مومیایی‌کنندگان | سرپرستان خط اول کارکنان خدمات شخصی | متصدیان مراسم تشییع | مدیران خانه تشییع | دستیاران سلامت در خانه | پرستاران عملی مجاز و پرستاران حرفه‌ای مجاز | مدیران خدمات پزشکی و بهداشتی | دستیاران پرستاری | نمایندگان بیمار | دستیاران مراقبت شخصی | مشاوران توانبخشی | مشاوران مسکونی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون | بازرسان مرگ | اپراتورهای کوره سوزاندن اجساد | مدیران، فعالیت‌ها و آموزش‌های مذهبی | مومیایی‌کنندگان | سرپرستان خط اول کارگران خدمات شخصی | متصدیان مراسم تشییع جنازه | مدیران خانه‌های تشییع جنازه | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | نمایندگان بیمار | کمک‌یاران مراقبت شخصی | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار برنامه‌ریزی قرار ملاقات | پایگاه‌های داده اطلاعات مشتریان | Facebook | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار پرداخت پایانه فروش POS | YouTube</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | پایگاه‌های داده اطلاعات مشتریان | Facebook | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار پرداخت پایانه فروش POS | YouTube</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و سازماندهی | زبان انگلیسی | اقتصاد و حسابداری | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | اقتصاد و حسابداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | درک شفاهی | بینایی نزدیک | زبردستی انگشتان | زبردستی دستی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | قدرت تنه | دقت کنترل | تجسم | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | درک شفاهی | بینایی نزدیک | مهارت انگشتان | مهارت دستی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | قدرت تنه | دقت کنترل | تجسم | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | صرف زمان به صورت ایستاده | گفتگوهای تلفنی | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | سطح رقابت | تاثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های چهره به چهره با افراد و در تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، با تهویه مطبوع</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | صرف زمان برای ایستادن | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول کارکنان خدمات شخصی | طراحان گل | پرداخت‌کاران مبلمان | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | جواهرسازان و سازندگان سنگ‌ها و فلزات قیمتی | کارکنان لباسشویی و خشک‌شویی | متصدیان رختکن، اتاق لباس و اتاق پرو | خدمتکاران و نظافتچی‌های خانه‌داری | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | نقاشان ساختمان و نگهداری | کارکنان نقاشی، پوشش‌دهی و تزئین | فروشندگان خرده‌فروشی | دوزندگان دستی | شامپوکاران | کارکنان و تعمیرکاران کفش و چرم | متخصصان مراقبت از پوست | مدیران اسپا | خیاطان، دوزندگان لباس و خیاطان سفارشی</t>
+          <t>سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران خدمات شخصی | طراحان گل | پرداخت‌کاران مبلمان | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارکنان خشک‌شویی و لباس‌شویی | متصدیان رختکن، اتاق لباس و اتاق پرو | خدمتکاران و تمیزکنندگان خانه‌داری | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | فروشندگان خرده‌فروشی | دوزندگان دستی | شامپوکاران | کارگران و تعمیرکاران کفش و چرم | متخصصان مراقبت از پوست | مدیران اسپا | خیاطان، دوزندگان زنانه و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apple iOS | نرم‌افزار برنامه‌ریزی قرار ملاقات | پایگاه‌های داده اطلاعات مشتریان | Facebook | Intuit QuickBooks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار پردازش فروش | YouTube</t>
+          <t>Apple iOS | نرم‌افزار زمان‌بندی قرار ملاقات | پایگاه‌های داده اطلاعات مشتریان | Facebook | Intuit QuickBooks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار پردازش فروش | YouTube</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | فروش و بازاریابی | مدیریت و سازماندهی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | زبردستی دستی | زبردستی انگشتان | درک شفاهی | اصالت | بیان شفاهی | تشخیص گفتار | تجسم | روانی ایده‌ها | وضوح گفتار | تشخیص رنگ بصری | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | درک شفاهی | اصالت | بیان شفاهی | تشخیص گفتار | تجسم | روانی ایده‌ها | وضوح گفتار | تشخیص رنگ بصری | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای تلفنی | بحث‌های چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | صرف زمان به صورت ایستاده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | داخل ساختمان، با تهویه مطبوع | اهمیت دقیق یا درست بودن | صرف زمان برای خم شدن یا پیچاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | سطح رقابت | سلامت و ایمنی سایر کارکنان</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | سطح رقابت | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آرایشگران مردانه | متصدیان لباس | طراحان مد | طراحان گل | پرداخت‌کاران مبلمان | جواهرسازان و سازندگان سنگ‌ها و فلزات قیمتی | کارکنان لباسشویی و خشک‌شویی | خدمتکاران و نظافتچی‌های خانه‌داری | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | عینک‌سازان تجویزی | نقاشان ساختمان و نگهداری | کارکنان نقاشی، پوشش‌دهی و تزئین | فروشندگان خرده‌فروشی | دوزندگان دستی | شامپوکاران | کارکنان و تعمیرکاران کفش و چرم | متخصصان مراقبت از پوست | مدیران اسپا | خیاطان، دوزندگان لباس و خیاطان سفارشی</t>
+          <t>آرایشگران مردانه | متصدیان لباس | طراحان مد | طراحان گل | پرداخت‌کاران مبلمان | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارکنان خشک‌شویی و لباس‌شویی | خدمتکاران و تمیزکنندگان خانه‌داری | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | عینک‌سازان، توزیع‌کننده | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | فروشندگان خرده‌فروشی | دوزندگان دستی | شامپوکاران | کارگران و تعمیرکاران کفش و چرم | متخصصان مراقبت از پوست | مدیران اسپا | خیاطان، دوزندگان زنانه و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | نرم‌افزار برنامه‌ریزی قرار ملاقات | Autodesk Maya | Autodesk Mudbox | نرم‌افزار وبلاگ‌نویسی | Bookitlive | Clear Books | پایگاه‌های داده مشتریان | DatInf DigiMakeup | نرم‌افزار ایمیل | Facebook | Instagram | Intuit QuickBooks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Pixologic Zbrush | SavingFace | Twitter | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Photoshop | نرم‌افزار زمان‌بندی قرار ملاقات | Autodesk Maya | Autodesk Mudbox | نرم‌افزار وبلاگ‌نویسی | Bookitlive | Clear Books | پایگاه‌های داده مراجعین | DatInf DigiMakeup | نرم‌افزار ایمیل | Facebook | Instagram | Intuit QuickBooks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Pixologic Zbrush | SavingFace | Twitter | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | هنرهای زیبا | طراحی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | هنرهای زیبا | طراحی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | تشخیص رنگ بصری | بیان شفاهی | ثبات دست و بازو | زبردستی انگشتان | زبردستی دستی | تجسم | اصالت | روانی ایده‌ها | درک کتبی | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | وضوح گفتار | بینایی دور | بیان کتبی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | درک شفاهی | تشخیص رنگ بصری | بیان شفاهی | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | تجسم | اصالت | روانی ایده‌ها | درک کتبی | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | وضوح گفتار | بینایی دور | بیان کتبی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | بحث‌های چهره به چهره با افراد و در تیم‌ها | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سطح رقابت | داخل ساختمان، با تهویه مطبوع | گفتگوهای تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان به صورت ایستاده | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فضای باز، زیر سقف | داخل ساختمان، بدون تهویه مطبوع</t>
+          <t>نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فضای باز، زیر سقف | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>آرایشگران مردانه | متصدیان لباس | هنرمندان صنایع دستی | حکاکان و قلم‌زنان | طراحان مد | هنرمندان هنرهای زیبا، از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل | طراحان گرافیک | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | جواهرسازان و سازندگان سنگ‌ها و فلزات قیمتی | مانیکوریست‌ها و پدیکوریست‌ها | مدل‌ها | نقاشان ساختمان و نگهداری | کارکنان نقاشی، پوشش‌دهی و تزئین | عکاسان | دوزندگان دستی | شامپوکاران | متخصصان مراقبت از پوست | هنرمندان جلوه‌های ویژه و انیماتورها | خیاطان، دوزندگان لباس و خیاطان سفارشی</t>
+          <t>آرایشگران مردانه | متصدیان لباس | هنرمندان صنایع دستی | حکاکان و تیزاب‌کاران | طراحان مد | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل | طراحان گرافیک | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | مانیکوریست‌ها و پدیکوریست‌ها | مدل‌ها | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | عکاسان | دوزندگان دستی | شامپوکاران | متخصصان مراقبت از پوست | هنرمندان جلوه‌های ویژه و انیماتورها | خیاطان، دوزندگان زنانه و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی</t>
+          <t>خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | زبردستی انگشتان | ثبات دست و بازو | تشخیص گفتار | زبردستی دستی | بیان شفاهی</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تشخیص گفتار | مهارت دستی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | داخل ساختمان، با تهویه مطبوع | صرف زمان به صورت نشسته | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | بحث‌های چهره به چهره با افراد و در تیم‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>آرایشگران مردانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌دهندگان و مرتب‌کنندگان دستی | تکنسین‌های آزمایشگاه دندان‌پزشکی | حکاکان و قلم‌زنان | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران مبلمان | کارکنان ساب‌زنی و صیقل‌کاری دستی | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | کارکنان لباسشویی و خشک‌شویی | میکاپ آرتیست‌های تئاتر و نمایش | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان ساختمان و نگهداری | کارکنان نقاشی، پوشش‌دهی و تزئین | دوزندگان دستی | شامپوکاران | اپراتورها و متصدیان ماشین کفش‌سازی | کارکنان و تعمیرکاران کفش و چرم | متخصصان مراقبت از پوست | تیزکنندگان و سوهان‌کاران ابزار</t>
+          <t>آرایشگران مردانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | برش‌دهندگان و پرداخت‌کاران دستی | تکنسین‌های پروتز دندان | حکاکان و تیزاب‌کاران | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | کارکنان خشک‌شویی و لباس‌شویی | میکاپ آرتیست‌های تئاتر و نمایش | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | دوزندگان دستی | شامپوکاران | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | متخصصان مراقبت از پوست | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار برنامه‌ریزی قرار ملاقات | نرم‌افزار ایمیل | Facebook | نرم‌افزار ردیابی موجودی | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار ایمیل | Facebook | نرم‌افزار ردیابی موجودی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | ثبات دست و بازو | زبردستی دستی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | ثبات دست و بازو | مهارت دستی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>داخل ساختمان، با تهویه مطبوع | ارتباط با دیگران | صرف زمان به صورت ایستاده | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره به چهره با افراد و در تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای تلفنی | آزادی در تصمیم‌گیری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | آرایشگران مردانه | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | دندان‌پزشکان عمومی | پزشکان طب اورژانس | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | دستیاران سلامت در خانه | کارکنان لباسشویی و خشک‌شویی | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | ماساژ درمانگران | دستیاران پرستاری | جراحان دهان، فک و صورت | جراحان ارتوپدی، به جز اطفال | جراحان اطفال | دستیاران فیزیوتراپیست | متخصصان مراقبت از پوست | دستیاران جراحی | تکنسین‌ها و تکنولوژیست‌های دامپزشکی</t>
+          <t>طب‌سوزنی‌ها | آرایشگران مردانه | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | دندانپزشکان، عمومی | پزشکان طب اورژانس | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | کمک‌یاران سلامت در منزل | کارکنان خشک‌شویی و لباس‌شویی | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | ماساژدرمانگران | کمک‌پرستاران | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | کمک‌یاران فیزیوتراپی | متخصصان مراقبت از پوست | دستیاران جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | فروش و بازاریابی | مدیریت و سازماندهی | آموزش و پرورش | زبان انگلیسی | اداری | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | اداری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | وضوح گفتار | درک کتبی | حساسیت به مسئله | ثبات دست و بازو | زبردستی انگشتان | توجه انتخابی | زبردستی دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بیان کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | وضوح گفتار | درک کتبی | حساسیت به مسئله | ثبات دست و بازو | مهارت انگشتان | توجه انتخابی | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | داخل ساختمان، با تهویه مطبوع | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای تلفنی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش‌های ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری یا عفونت‌ها | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سطح رقابت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | آرایشگران مردانه | دستیاران دندان‌پزشکی | دندان‌پزشکان عمومی | متخصصان پوست | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | ماساژ درمانگران | دستیاران پزشکی | اپتومتریست‌ها | جراحان دهان، فک و صورت | جراحان اطفال | دستیاران فیزیوتراپیست | متخصصان بیماری‌های پا | متخصصان پروتزهای دندانی | شامپوکاران | مدیران اسپا | دستیاران جراحی | تکنسین‌های جراحی</t>
+          <t>طب‌سوزنی‌ها | آرایشگران مردانه | دستیاران دندان‌پزشکی | دندانپزشکان، عمومی | متخصصان پوست | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | میکاپ آرتیست‌های تئاتر و نمایش | مانیکوریست‌ها و پدیکوریست‌ها | ماساژدرمانگران | دستیاران پزشکی | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان کودکان | کمک‌یاران فیزیوتراپی | پزشکان پا | متخصصان پروتز دندان | شامپوکاران | مدیران اسپا | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | حمل و نقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | حمل و نقل</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | قدرت تنه | تشخیص گفتار | قدرت ایستا | هماهنگی چند عضو | وضوح گفتار | انعطاف‌پذیری بدنی | استقامت | اشتراک زمانی | توجه انتخابی | حساسیت به مسئله | بینایی نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | قدرت تنه | تشخیص گفتار | قدرت ایستا | هماهنگی چند عضو | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | استقامت | تقسیم توجه | توجه انتخابی | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | داخل ساختمان، با تهویه مطبوع | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای تلفنی | صرف زمان به صورت ایستاده | بحث‌های چهره به چهره با افراد و در تیم‌ها | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | متصدیان تفریح و سرگرمی | رانندگان اتوبوس، ترانزیت و بین شهری | صندوق‌داران | کانسرج‌ها | متصدیان باجه و اجاره | پیک‌ها و نامه‌رسان‌ها | متصدیان سالن غذاخوری و کافه تریا و دستیاران بارتندر | دیسپچرهای به جز پلیس، آتش‌نشانی و آمبولانس | مهمانداران هواپیما | سروکنندگان غذا، غیررستورانی | کارمندان پذیرش هتل، متل و تفریحگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | متصدیان پارکینگ | متصدیان مسافر | ماموران فروش بلیط رزرو و حمل و نقل و کارمندان سفر | رانندگان شاتل و شوفرها | انبارداران و پرکنندگان سفارش | ماموران غربالگری امنیت حمل و نقل | راهنمایان، متصدیان لابی و بلیط‌گیرها</t>
+          <t>سرپرستان جابجایی بار هواپیما | متصدیان تفریح و سرگرمی | رانندگان اتوبوس، ترانزیت و بین‌شهری | صندوق‌داران | کانسرج‌ها | کارمندان باجه و اجاره | پیک‌ها و نامه‌رسان‌ها | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مهمانداران هواپیما | سروکنندگان غذا، غیررستورانی | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | متصدیان پارکینگ | متصدیان مسافران | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | رانندگان شاتل و شوفرها | قفسه‌چین‌ها و پرکننده‌های سفارش | غربالگران امنیتی حمل و نقل | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار صدور صورت‌حساب | نرم‌افزار بودجه‌بندی | Delphi Technology | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار | نرم‌افزار Yardi</t>
+          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار بودجه‌بندی | Delphi Technology | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | حمل و نقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | بحث‌های چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | داخل ساختمان، با تهویه مطبوع | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>باربران چمدان و پادوهای هتل | متصدیان باجه و اجاره | کارشناسان خدمات مشتریان | متصدیان سالن غذاخوری و کافه تریا و دستیاران بارتندر | مهمانداران هواپیما | سروکنندگان غذا، غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و تفریحگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | خدمتکاران و نظافتچی‌های خانه‌داری | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | متصدیان پارکینگ | متصدیان مسافر | متصدیان پذیرش و اطلاعات | ماموران فروش بلیط رزرو و حمل و نقل و کارمندان سفر | کارگزاران مسافرتی | راهنمایان سفر | راهنمایان، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌های رستوران</t>
+          <t>باربران چمدان و پادوهای هتل | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | مهمانداران هواپیما | سروکنندگان غذا، غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | خدمتکاران و تمیزکنندگان خانه‌داری | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | متصدیان پارکینگ | متصدیان مسافران | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | آژانس‌های مسافرتی | راهنمایان سفر | راهنماها، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | تاریخ و باستان‌شناسی | ارتباطات و رسانه | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تاریخ و باستان‌شناسی | ارتباطات و رسانه | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>سخنرانی عمومی | بحث‌های چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>سخنرانی عمومی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | کانسرج‌ها | کیوریتورها | مدیران سرگرمی و تفریح، به جز قمار | سرپرستان خط اول کارکنان سرگرمی و تفریح، به جز خدمات قمار | مورخان | معلمان تاریخ، تحصیلات عالی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | طبیعی‌دانان پارک | کارکنان تفریحی | ماموران فروش بلیط رزرو و حمل و نقل و کارمندان سفر | معلمان خودشکوفایی | دستیاران آموزشی، آموزش استثنایی | کارگزاران مسافرتی | راهنمایان سفر | راهنمایان، متصدیان لابی و بلیط‌گیرها</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | کانسرج‌ها | موزه‌داران | مدیران سرگرمی و تفریح، به جز قماربازی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | مورخان | مدرسان تاریخ، آموزش عالی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | طبیعت‌شناسان پارک | کارکنان تفریحات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | معلمان خودسازی | دستیاران آموزشی، آموزش استثنایی | آژانس‌های مسافرتی | راهنمایان سفر | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0061_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0061_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | مدیریت و امور اداری | روان‌شناسی | امور کارکنان و منابع انسانی | رایانه و الکترونیک | فروش و بازاریابی | زیست‌شناسی | فلسفه و الهیات | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | مدیریت و اداره | روان‌شناسی | پرسنل و منابع انسانی | رایانه و الکترونیک | فروش و بازاریابی | زیست‌شناسی | فلسفه و الهیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | توجه انتخابی | استدلال قیاسی | روانی کلام و سیالی ایده‌ها | بیان کتبی | درک کتبی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | ابتکار و اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | استدلال قیاسی | روانی ایده‌ها | بیان کتبی | درک کتبی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون و مبلغان مذهبی | پزشکان قانونی | متصدیان کوره‌های جسدسوزی | مدیران فعالیت‌ها و آموزش‌های مذهبی | متصدیان مومیایی و آماده‌سازی اجساد | سرپرستان رده‌اول کارکنان خدمات فردی | متصدیان و خدمه سالن‌های ترحیم | مدیران آرامستان‌ها و سالن‌های ترحیم | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مدیران خدمات بهداشتی و درمانی | کمک‌بهیاران | نمایندگان و رابطان بیماران | مراقبان و دستیاران خدمات فردی | مشاوران توانبخشی | سرپرستان خوابگاه‌ها و اقامتگاه‌ها | منشی‌ها و مسئولان دفاتر اداری به‌جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روحانیون و مبلغان مذهبی | پزشکان قانونی و بازرسان مرگ مشکوک | اپراتورهای کوره‌های سوزاندن جسد | مدیران فعالیت‌ها و آموزش‌های مذهبی | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | متصدیان و دستیاران خدمات مراسم ترحیم | مدیران آرامستان‌ها و امور خدمات متوفیات | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مدیران خدمات درمانی و بهداشتی | کمک‌پرستاران | کارشناسان امور بیماران و پذیرش | مراقبان خدمات شخصی و همراهان توان‌خواهان | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | منشی‌ها و دستیاران اداری عمومی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | اقتصاد و حسابداری | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | اقتصاد و حسابداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | درک شفاهی | دید نزدیک | چابکی انگشتان | چابکی دستی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | قدرت عضلات تنه | دقت کنترل حرکتی | تجسم فضایی | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | درک شفاهی | بینایی نزدیک | مهارت انگشتان | مهارت دستی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | توجه انتخابی | قدرت تنه | دقت کنترل | تجسم | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول نیروهای خدمات و نظافت | سرپرستان رده‌اول کارکنان خدمات فردی | طراحان گل و گل‌آراها | پرداخت‌کاران چوب و مبلمان | آرایشگران، پیرایشگران و متخصصان زیبایی زنان | سازندگان طلا و جواهر و سنگ‌های قیمتی | کارگران خشکشویی و لاندری | متصدیان رختکن و اتاق تعویض لباس | خدمتکاران و نظافتچیان اماکن | گریموران و چهره‌پردازان تئاتر و سینما | ناخن‌کاران و تکنسین‌های مانیکور و پدیکور | نقاشان ساختمان و کارهای تعمیراتی | رنگ‌کاران و تزیین‌کاران سطوح | فروشندگان خرده‌فروشی | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | کارگران و تعمیرکاران کفش و کالاهای چرمی | متخصصان و تکنسین‌های مراقبت از پوست | مدیران سالن‌های اسپا و ماساژ | خیاطان زنانه، مردانه و شخصی‌دوز</t>
+          <t>سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | طراحان گل و گل‌آراها | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | آرایشگران و متخصصان زیبایی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | متصدیان رختکن، امانات و اتاق پرو | خدمتکاران و نظافتچیان منازل و هتل‌ها | چهره‌پردازان و گریموران تئاتر و سینما | ناخن‌کاران و متخصصان مانیکور و پدیکور | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | فروشندگان خرده‌فروشی | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | کارگران و تعمیرکاران کفش و چرم | متخصصان و تکنسین‌های مراقبت از پوست | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | درک شفاهی | ابتکار و اصالت | بیان شفاهی | تشخیص گفتار | تجسم فضایی | روانی کلام و سیالی ایده‌ها | وضوح گفتار | تشخیص تمایز رنگ‌ها | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | درک شفاهی | اصالت | بیان شفاهی | تشخیص گفتار | تجسم | روانی ایده‌ها | وضوح گفتار | تشخیص رنگ بصری | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پیرایشگران مردانه | مسئولان و متصدیان لباس صحنه | طراحان مد و لباس | طراحان گل و گل‌آراها | پرداخت‌کاران چوب و مبلمان | سازندگان طلا و جواهر و سنگ‌های قیمتی | کارگران خشکشویی و لاندری | خدمتکاران و نظافتچیان اماکن | گریموران و چهره‌پردازان تئاتر و سینما | ناخن‌کاران و تکنسین‌های مانیکور و پدیکور | عینک‌سازان (ساخت و فروش عینک) | نقاشان ساختمان و کارهای تعمیراتی | رنگ‌کاران و تزیین‌کاران سطوح | فروشندگان خرده‌فروشی | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | کارگران و تعمیرکاران کفش و کالاهای چرمی | متخصصان و تکنسین‌های مراقبت از پوست | مدیران سالن‌های اسپا و ماساژ | خیاطان زنانه، مردانه و شخصی‌دوز</t>
+          <t>پیرایشگران مردانه | متصدیان و جامه داران لباس صحنه | طراحان مد و پوشاک | طراحان گل و گل‌آراها | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | خدمتکاران و نظافتچیان منازل و هتل‌ها | چهره‌پردازان و گریموران تئاتر و سینما | ناخن‌کاران و متخصصان مانیکور و پدیکور | عینک‌سازان (ساخت و فروش عینک) | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | فروشندگان خرده‌فروشی | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | کارگران و تعمیرکاران کفش و چرم | متخصصان و تکنسین‌های مراقبت از پوست | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | هنرهای تجسمی | طراحی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | هنرهای زیبا | طراحی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | تشخیص تمایز رنگ‌ها | بیان شفاهی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | تجسم فضایی | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | درک کتبی | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی | وضوح گفتار | دید دور | بیان کتبی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | درک شفاهی | تشخیص رنگ بصری | بیان شفاهی | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | تجسم | اصالت | روانی ایده‌ها | درک کتبی | تشخیص گفتار | حساسیت به مسئله | توجه انتخابی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | وضوح گفتار | بینایی دور | بیان کتبی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پیرایشگران مردانه | مسئولان و متصدیان لباس صحنه | هنرمندان صنایع دستی | قلم‌زنان و حکاکان | طراحان مد و لباس | هنرمندان هنرهای تجسمی از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل و گل‌آراها | طراحان گرافیک | آرایشگران، پیرایشگران و متخصصان زیبایی زنان | سازندگان طلا و جواهر و سنگ‌های قیمتی | ناخن‌کاران و تکنسین‌های مانیکور و پدیکور | مدل‌ها و مانکن‌ها | نقاشان ساختمان و کارهای تعمیراتی | رنگ‌کاران و تزیین‌کاران سطوح | عکاسان | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | متخصصان و تکنسین‌های مراقبت از پوست | هنرمندان جلوه‌های ویژه و پویانماها | خیاطان زنانه، مردانه و شخصی‌دوز</t>
+          <t>پیرایشگران مردانه | متصدیان و جامه داران لباس صحنه | هنرمندان صنایع دستی | حکاکان و اسیدکاران | طراحان مد و پوشاک | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گل و گل‌آراها | طراحان گرافیک | آرایشگران و متخصصان زیبایی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | ناخن‌کاران و متخصصان مانیکور و پدیکور | مدل‌ها | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | عکاسان | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | متخصصان و تکنسین‌های مراقبت از پوست | پویانماها و طراحان جلوه‌های ویژه | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی</t>
+          <t>خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | ثبات دست و بازو | تشخیص گفتار | چابکی دستی | بیان شفاهی</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تشخیص گفتار | مهارت دستی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پیرایشگران مردانه | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات رنگ‌پاشی و پوشش‌دهی | برش‌کاران دستی مواد و الگوها | تکنسین‌های پروتزهای دندانی (دندانسازان) | قلم‌زنان و حکاکان | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران چوب و مبلمان | سنگ‌زنان و پرداخت‌کاران دستی | آرایشگران، پیرایشگران و متخصصان زیبایی زنان | کارگران خشکشویی و لاندری | گریموران و چهره‌پردازان تئاتر و سینما | قالب‌ریزان و شکل‌دهندگان به‌جز فلزات و پلاستیک | نقاشان ساختمان و کارهای تعمیراتی | رنگ‌کاران و تزیین‌کاران سطوح | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | اپراتورهای ماشین‌های کفش‌دوزی | کارگران و تعمیرکاران کفش و کالاهای چرمی | متخصصان و تکنسین‌های مراقبت از پوست | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار</t>
+          <t>پیرایشگران مردانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | برشکاران و پیرایشگران دستی | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | حکاکان و اسیدکاران | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | آرایشگران و متخصصان زیبایی | کارگران خشکشویی و رختشویخانه | چهره‌پردازان و گریموران تئاتر و سینما | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | دوزندگان دستی | متصدیان شست‌وشوی مو و سر | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | متخصصان و تکنسین‌های مراقبت از پوست | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار نوبت‌دهی و زمان‌بندی | نرم‌افزار ایمیل | نرم‌افزار مدیریت و پیگیری موجودی | نرم‌افزار مرورگر وب | Facebook</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار ایمیل | Facebook | نرم‌افزار مرورگر وب | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | ثبات دست و بازو | چابکی دستی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | ثبات دست و بازو | مهارت دستی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | پیرایشگران مردانه | دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | دندان‌پزشکان عمومی | پزشکان طب اورژانس | آرایشگران، پیرایشگران و متخصصان زیبایی زنان | مراقبان سلامت در منزل | کارگران خشکشویی و لاندری | گریموران و چهره‌پردازان تئاتر و سینما | ناخن‌کاران و تکنسین‌های مانیکور و پدیکور | ماساژورها و ماساژدرمانگران | کمک‌بهیاران | جراحان دهان، فک و صورت | جراحان ارتوپدی به‌جز اطفال | جراحان کودکان | کمک‌کارشناسان و دستیاران فیزیوتراپی | متخصصان و تکنسین‌های مراقبت از پوست | دستیاران جراحی | کارشناسان و تکنسین‌های دامپزشکی</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پیرایشگران مردانه | دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | دندان‌پزشکان عمومی | پزشکان طب اورژانس | آرایشگران و متخصصان زیبایی | مراقبان سلامت و بهیاران مراقبت در منزل | کارگران خشکشویی و رختشویخانه | چهره‌پردازان و گریموران تئاتر و سینما | ناخن‌کاران و متخصصان مانیکور و پدیکور | ماساژدرمانگران | کمک‌پرستاران | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | کمک‌یاران فیزیوتراپی | متخصصان و تکنسین‌های مراقبت از پوست | دستیاران جراحی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مدیریت و امور اداری | آموزش و تدریس | زبان انگلیسی | امور اداری و دفتری | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | آموزش و پرورش | زبان انگلیسی | اداری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | وضوح گفتار | درک کتبی | حساسیت به مسئله | ثبات دست و بازو | چابکی انگشتان | توجه انتخابی | چابکی دستی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | روانی کلام و سیالی ایده‌ها | بیان کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | وضوح گفتار | درک کتبی | حساسیت به مسئله | ثبات دست و بازو | مهارت انگشتان | توجه انتخابی | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | پیرایشگران مردانه | دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | پزشکان متخصص پوست و مو | آرایشگران، پیرایشگران و متخصصان زیبایی زنان | گریموران و چهره‌پردازان تئاتر و سینما | ناخن‌کاران و تکنسین‌های مانیکور و پدیکور | ماساژورها و ماساژدرمانگران | دستیاران پزشک | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان کودکان | کمک‌کارشناسان و دستیاران فیزیوتراپی | متخصصان درمان بیماری‌های پا (پودیاتریست‌ها) | متخصصان پروتزهای دندانی | متصدیان شست‌وشوی مو و سر | مدیران سالن‌های اسپا و ماساژ | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پیرایشگران مردانه | دستیاران دندان‌پزشک | دندان‌پزشکان عمومی | متخصصان پوست و مو | آرایشگران و متخصصان زیبایی | چهره‌پردازان و گریموران تئاتر و سینما | ناخن‌کاران و متخصصان مانیکور و پدیکور | ماساژدرمانگران | کمک‌پزشکان و دستیاران مطب | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان اطفال | کمک‌یاران فیزیوتراپی | پزشکان متخصص پا و مچ پا | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | متصدیان شست‌وشوی مو و سر | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار Corel WordPerfect Office Suite | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار Microsoft Word</t>
+          <t>Corel WordPerfect Office Suite | نرم‌افزار Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook | نرم‌افزار Microsoft Word</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | حمل‌ونقل و ترابری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | حمل و نقل</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | قدرت عضلات تنه | تشخیص گفتار | قدرت بدنی ایستا | هماهنگی اندام‌های حرکتی | وضوح گفتار | انعطاف‌پذیری بدنی | استقامت و تحمل جسمانی | مدیریت و تقسیم توجه | توجه انتخابی | حساسیت به مسئله | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | قدرت تنه | تشخیص گفتار | قدرت ایستا | هماهنگی چند عضو | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | استقامت | تقسیم توجه | توجه انتخابی | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان خدمات تفریحی و سرگرمی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | صندوقداران | متصدیان تشریفات و راهنمای میهمانان (کانسیرژ) | کارمندان پذیرش، باجه و اجاره کالا | پیک‌ها، نامه‌رسان‌ها و نامه‌بران | نیروهای پذیرایی سالن غذاخوری، سلف‌سرویس و کمک‌باریستاها | متصدیان اعزام و دیسپچری به‌جز پلیس، آتش‌نشانی و اورژانس | مهمانداران هواپیما | متصدیان پذیرایی و توزیع غذا در مراکز غیررستورانی | کارمندان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان رختکن و اتاق تعویض لباس | پارکبان‌ها و مسئولان پارکینگ | متصدیان و مأموران خدمات مسافران | کارمندان رزرواسیون، فروش بلیط و خدمات سفر | رانندگان خودروهای تشریفاتی و سرویس‌های شاتل | کارگران چیدمان و جمع‌آوری سفارش‌ها در انبار | بازرسان و مأموران حراست و بازرسی امنیت پرواز | راهنمایان سالن، متصدیان لابی و بلیط‌گیرها</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان اماکن تفریحی و شهربازی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | صندوق‌داران | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | پیک‌ها و نامه‌رسان‌ها | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | متصدیان دیسپاچ و اعزام | مهمانداران هواپیما | سروکنندگان غذا در محیط‌های غیررستورانی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | رانندگان خودروهای سرویس و تشریفات | متصدیان چیدمان و آماده‌سازی سفارش | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | حمل‌ونقل و ترابری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | بیان کتبی | درک کتبی | دید نزدیک | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | بیان کتبی | درک کتبی | بینایی نزدیک | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان حمل بار و خدمات هتل | کارمندان پذیرش، باجه و اجاره کالا | کارشناسان و نمایندگان خدمات مشتریان | نیروهای پذیرایی سالن غذاخوری، سلف‌سرویس و کمک‌باریستاها | مهمانداران هواپیما | متصدیان پذیرایی و توزیع غذا در مراکز غیررستورانی | میزبانان و پذیرشگران رستوران، لانج و کافی‌شاپ | کارمندان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان رختکن و اتاق تعویض لباس | مدیران مراکز اقامتی و هتل‌ها | خدمتکاران و نظافتچیان اماکن | برنامه‌ریزان همایش‌ها، کنفرانس‌ها و رویدادها | پارکبان‌ها و مسئولان پارکینگ | متصدیان و مأموران خدمات مسافران | مسئولان پذیرش و دفاتر اطلاعات | کارمندان رزرواسیون، فروش بلیط و خدمات سفر | متصدیان آژانس‌های مسافرتی | راهنمایان تور و سفر | راهنمایان سالن، متصدیان لابی و بلیط‌گیرها | گارسون‌ها و پیشخدمت‌های رستوران</t>
+          <t>متصدیان حمل بار و خدمات هتل | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | مهمانداران هواپیما | سروکنندگان غذا در محیط‌های غیررستورانی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | مدیران هتل و مراکز اقامتی | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | کارشناسان و دفاتر خدمات مسافرتی و جهانگردی | راهنمایان گردشگری و تور | راهنماها، متصدیان سالن و بلیط‌گیرها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | تاریخ و باستان‌شناسی | ارتباطات و رسانه | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تاریخ و باستان‌شناسی | ارتباطات و رسانه | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | درک کتبی | دید دور | دید نزدیک | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | درک کتبی | بینایی دور | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدرسان آموزش پایه بزرگسالان، متوسطه و زبان دوم | متصدیان خدمات تفریحی و سرگرمی | متصدیان حمل بار و خدمات هتل | متصدیان تشریفات و راهنمای میهمانان (کانسیرژ) | موزه‌داران و موزه‌ورزان | مدیران امور تفریحی، ورزشی و سرگرمی به‌جز قمار | سرپرستان رده‌اول کارکنان مراکز تفریحی به‌جز بازی‌های شرط‌بندی | تاریخ‌نگاران و پژوهشگران تاریخ | اساتید و مدرسان تاریخ در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | کتابداران و متخصصان آرشیو رسانه‌ای | برنامه‌ریزان همایش‌ها، کنفرانس‌ها و رویدادها | کارشناسان و مروجان طبیعت و پارک‌های ملی | کارکنان امور اوقات فراغت و تفریحی | کارمندان رزرواسیون، فروش بلیط و خدمات سفر | مربیان و مدرسان دوره‌های آزاد مهارتی | دستیاران آموزشی در حوزه آموزش استثنایی | متصدیان آژانس‌های مسافرتی | راهنمایان تخصصی سفر و بوم‌گردی | راهنمایان سالن، متصدیان لابی و بلیط‌گیرها</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | متصدیان اماکن تفریحی و شهربازی | متصدیان حمل بار و خدمات هتل | متصدیان تشریفات و خدمات میهمانان | موزه‌داران | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مورخان | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | طبیعت‌شناسان و کارشناسان پارک‌های ملی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | کمک‌معلمان آموزش استثنایی | کارشناسان و دفاتر خدمات مسافرتی و جهانگردی | راهنمایان گردشگری و تور | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
